--- a/trips/Trips.xlsx
+++ b/trips/Trips.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\Snippets\trips\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\Snippets\tester\trips\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>Formulario con Gasto y Monto Total</t>
   </si>
@@ -122,9 +122,6 @@
     <t>Tabla de Base de Datos =&gt; NOMBRE_PAIS (FRANCIA)</t>
   </si>
   <si>
-    <t>x</t>
-  </si>
-  <si>
     <t>IVA y BASE generados con PHP</t>
   </si>
   <si>
@@ -135,6 +132,12 @@
   </si>
   <si>
     <t>NOMBRE:_________________________</t>
+  </si>
+  <si>
+    <t>*OTROS</t>
+  </si>
+  <si>
+    <t>CSS en archivo aparte</t>
   </si>
   <si>
     <r>
@@ -149,14 +152,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>ESPAÑA</t>
+      <t>FRANCIA</t>
     </r>
-  </si>
-  <si>
-    <t>*OTROS</t>
-  </si>
-  <si>
-    <t>CSS en archivo aparte</t>
   </si>
 </sst>
 </file>
@@ -253,13 +250,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -556,397 +553,321 @@
   <sheetData>
     <row r="1" spans="3:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C3" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
+      <c r="C3" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
     </row>
     <row r="5" spans="3:6" x14ac:dyDescent="0.4">
       <c r="C5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C7" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C11" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="7"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="7"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C15" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C16" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C17" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="7"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C18" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="7"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C19" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="7"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="21" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C21" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+    </row>
+    <row r="22" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C22" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="7"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C23" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="7"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C24" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="7"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C25" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="7"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="7"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C27" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="7"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="29" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C29" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+    </row>
+    <row r="30" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C30" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="7"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C31" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="7"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C32" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="7"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C33" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="7"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" s="7"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C35" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="7"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C36" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="7"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="6"/>
+    </row>
+    <row r="39" spans="3:6" x14ac:dyDescent="0.4">
+      <c r="C39" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C7" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-    </row>
-    <row r="8" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C8" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C9" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C10" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C11" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C12" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C13" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C14" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C15" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C16" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C17" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C18" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C19" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C21" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-    </row>
-    <row r="22" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C22" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="8"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C23" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="8"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C24" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C25" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C26" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C27" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="8"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C29" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-    </row>
-    <row r="30" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C30" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D30" s="8"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="31" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C31" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D31" s="8"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C32" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="8"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C33" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D33" s="8"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C34" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D34" s="8"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="35" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C35" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D35" s="8"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="36" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C36" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" s="8"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="39" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C39" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
     </row>
     <row r="40" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D40" s="8"/>
+      <c r="D40" s="7"/>
       <c r="E40" s="5"/>
       <c r="F40" s="6"/>
     </row>
     <row r="41" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D41" s="8"/>
+      <c r="D41" s="7"/>
       <c r="E41" s="5"/>
       <c r="F41" s="6"/>
     </row>
     <row r="42" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D42" s="8"/>
+      <c r="D42" s="7"/>
       <c r="E42" s="5"/>
       <c r="F42" s="6"/>
     </row>
     <row r="43" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C43" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D43" s="8"/>
+      <c r="C43" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D43" s="7"/>
       <c r="E43" s="5"/>
       <c r="F43" s="6"/>
     </row>
     <row r="44" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C44" s="8" t="s">
+      <c r="C44" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D44" s="8"/>
+      <c r="D44" s="7"/>
       <c r="E44" s="5"/>
       <c r="F44" s="6"/>
     </row>
     <row r="45" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D45" s="8"/>
+      <c r="D45" s="7"/>
       <c r="E45" s="5"/>
       <c r="F45" s="6"/>
     </row>
     <row r="46" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
       <c r="E46" s="5"/>
       <c r="F46" s="6"/>
     </row>
     <row r="47" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
       <c r="E47" s="5"/>
       <c r="F47" s="6"/>
     </row>
     <row r="48" spans="3:6" x14ac:dyDescent="0.4">
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
       <c r="E48" s="5"/>
       <c r="F48" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C39:F39"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="C27:D27"/>
@@ -960,6 +881,32 @@
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="55" orientation="portrait" r:id="rId1"/>
